--- a/12609198.xlsx
+++ b/12609198.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b6f77ca67a4eaafc/Pictures/Desktop/demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47A625E3-0259-47D1-9ACB-AA46EFC4EEE3}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56CF4CEC-C1C2-416E-B9C2-439769E55123}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -212,6 +212,39 @@
   </si>
   <si>
     <t>Felt a bit tired after evening class.</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>feeling tired after playing football.</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>relaxed and enjoy free time</t>
+  </si>
+  <si>
+    <t>went to market for shopping</t>
+  </si>
+  <si>
+    <t>balanced day with good activity</t>
+  </si>
+  <si>
+    <t>good study and coding progress</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>felt tired after a busy day</t>
+  </si>
+  <si>
+    <t>finished the day with good energy</t>
+  </si>
+  <si>
+    <t>spend quality time with friends</t>
   </si>
 </sst>
 </file>
@@ -1040,9 +1073,9 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B7" s="14">
         <v>420</v>
@@ -1057,24 +1090,22 @@
         <v>60</v>
       </c>
       <c r="F7" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G7" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H7" s="14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I7" s="15">
-        <f t="shared" si="0"/>
-        <v>920</v>
+        <v>990</v>
       </c>
       <c r="J7" s="15">
-        <f t="shared" si="1"/>
-        <v>520</v>
+        <v>450</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="L7" s="16" t="s">
         <v>57</v>
@@ -1088,7 +1119,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B8" s="14">
         <v>480</v>
@@ -1100,189 +1131,343 @@
         <v>120</v>
       </c>
       <c r="E8" s="14">
+        <v>120</v>
+      </c>
+      <c r="F8" s="14">
+        <v>250</v>
+      </c>
+      <c r="G8" s="14">
+        <v>5</v>
+      </c>
+      <c r="H8" s="14">
         <v>60</v>
       </c>
-      <c r="F8" s="14">
+      <c r="I8" s="15">
+        <v>1090</v>
+      </c>
+      <c r="J8" s="15">
+        <v>350</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B9" s="14">
+        <v>480</v>
+      </c>
+      <c r="C9" s="14">
+        <v>60</v>
+      </c>
+      <c r="D9" s="14">
+        <v>180</v>
+      </c>
+      <c r="E9" s="14">
+        <v>120</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>120</v>
+      </c>
+      <c r="I9" s="15">
+        <v>960</v>
+      </c>
+      <c r="J9" s="15">
+        <v>480</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B10" s="14">
+        <v>420</v>
+      </c>
+      <c r="C10" s="14">
+        <v>60</v>
+      </c>
+      <c r="D10" s="14">
+        <v>240</v>
+      </c>
+      <c r="E10" s="14">
+        <v>90</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>120</v>
+      </c>
+      <c r="I10" s="15">
+        <v>930</v>
+      </c>
+      <c r="J10" s="15">
+        <v>510</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B11" s="14">
+        <v>360</v>
+      </c>
+      <c r="C11" s="14">
+        <v>60</v>
+      </c>
+      <c r="D11" s="14">
+        <v>120</v>
+      </c>
+      <c r="E11" s="14">
+        <v>60</v>
+      </c>
+      <c r="F11" s="14">
         <v>300</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G11" s="14">
         <v>6</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H11" s="14">
         <v>30</v>
       </c>
-      <c r="I8" s="15">
-        <v>1050</v>
-      </c>
-      <c r="J8" s="15">
-        <v>390</v>
-      </c>
-      <c r="K8" s="16" t="s">
+      <c r="I11" s="15">
+        <v>930</v>
+      </c>
+      <c r="J11" s="15">
+        <v>510</v>
+      </c>
+      <c r="K11" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B12" s="14">
+        <v>360</v>
+      </c>
+      <c r="C12" s="14">
+        <v>60</v>
+      </c>
+      <c r="D12" s="14">
+        <v>120</v>
+      </c>
+      <c r="E12" s="14">
+        <v>90</v>
+      </c>
+      <c r="F12" s="14">
+        <v>200</v>
+      </c>
+      <c r="G12" s="14">
+        <v>4</v>
+      </c>
+      <c r="H12" s="14">
+        <v>30</v>
+      </c>
+      <c r="I12" s="15">
+        <v>860</v>
+      </c>
+      <c r="J12" s="15">
+        <v>580</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B13" s="14">
+        <v>420</v>
+      </c>
+      <c r="C13" s="14">
+        <v>60</v>
+      </c>
+      <c r="D13" s="14">
+        <v>90</v>
+      </c>
+      <c r="E13" s="14">
+        <v>60</v>
+      </c>
+      <c r="F13" s="14">
+        <v>400</v>
+      </c>
+      <c r="G13" s="14">
+        <v>8</v>
+      </c>
+      <c r="H13" s="14">
+        <v>30</v>
+      </c>
+      <c r="I13" s="15">
+        <v>1060</v>
+      </c>
+      <c r="J13" s="15">
+        <v>380</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L13" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="M8" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+      <c r="M13" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+      <c r="A14" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B14" s="14">
+        <v>420</v>
+      </c>
+      <c r="C14" s="14">
+        <v>60</v>
+      </c>
+      <c r="D14" s="14">
+        <v>240</v>
+      </c>
+      <c r="E14" s="14">
+        <v>120</v>
+      </c>
+      <c r="F14" s="14">
+        <v>200</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="14">
+        <v>60</v>
+      </c>
+      <c r="I14" s="15">
+        <v>1100</v>
+      </c>
+      <c r="J14" s="15">
+        <v>340</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+      <c r="A15" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B15" s="14">
+        <v>420</v>
+      </c>
+      <c r="C15" s="14">
+        <v>60</v>
+      </c>
+      <c r="D15" s="14">
+        <v>90</v>
+      </c>
+      <c r="E15" s="14">
+        <v>90</v>
+      </c>
+      <c r="F15" s="14">
+        <v>250</v>
+      </c>
+      <c r="G15" s="14">
+        <v>5</v>
+      </c>
+      <c r="H15" s="14">
+        <v>60</v>
+      </c>
+      <c r="I15" s="15">
+        <v>970</v>
+      </c>
+      <c r="J15" s="15">
+        <v>470</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
